--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run2/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run2/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9906,0.0014,0.0041,0.0005</t>
-  </si>
-  <si>
-    <t>0.0193,0.0024,0.0001,0.9925</t>
-  </si>
-  <si>
-    <t>0.8467,0.0093,0.0007,0.1190</t>
-  </si>
-  <si>
-    <t>0.3865,0.0010,0.0005,0.8674</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9973,0.0007,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0001,0.0000,0.0013</t>
-  </si>
-  <si>
-    <t>0.9931,0.0034,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9921,0.0064,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.8133,0.0265,0.2220,0.0012</t>
-  </si>
-  <si>
-    <t>0.0096,0.0080,0.9830,0.0041</t>
-  </si>
-  <si>
-    <t>0.6708,0.0047,0.5609,0.0001</t>
-  </si>
-  <si>
-    <t>0.0260,0.0239,0.9518,0.0058</t>
-  </si>
-  <si>
-    <t>0.9555,0.0057,0.0623,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.9990,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.0066,0.9905,0.0044,0.0008</t>
-  </si>
-  <si>
-    <t>0.3744,0.6777,0.0296,0.0017</t>
-  </si>
-  <si>
-    <t>0.0058,0.9926,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.9963,0.0172,0.0001</t>
-  </si>
-  <si>
-    <t>0.9308,0.0013,0.0840,0.0010</t>
-  </si>
-  <si>
-    <t>0.9284,0.0048,0.0790,0.0005</t>
-  </si>
-  <si>
-    <t>0.0040,0.0009,0.9929,0.0008</t>
-  </si>
-  <si>
-    <t>0.0554,0.0110,0.9371,0.0054</t>
-  </si>
-  <si>
-    <t>0.1349,0.0054,0.9316,0.0006</t>
-  </si>
-  <si>
-    <t>0.0842,0.0022,0.9503,0.0006</t>
-  </si>
-  <si>
-    <t>0.0136,0.0007,0.9884,0.0003</t>
-  </si>
-  <si>
-    <t>0.7971,0.2888,0.0118,0.0019</t>
-  </si>
-  <si>
-    <t>0.6329,0.2613,0.1510,0.0041</t>
-  </si>
-  <si>
-    <t>0.0352,0.0292,0.9501,0.0103</t>
-  </si>
-  <si>
-    <t>0.0131,0.9680,0.0145,0.0008</t>
-  </si>
-  <si>
-    <t>0.9774,0.0116,0.0020,0.0031</t>
-  </si>
-  <si>
-    <t>0.6443,0.1729,0.2129,0.0123</t>
-  </si>
-  <si>
-    <t>0.2676,0.8548,0.0048,0.0004</t>
-  </si>
-  <si>
-    <t>0.0062,0.9902,0.0250,0.0003</t>
-  </si>
-  <si>
-    <t>0.3279,0.2555,0.2490,0.0492</t>
-  </si>
-  <si>
-    <t>0.8675,0.0022,0.1456,0.0040</t>
-  </si>
-  <si>
-    <t>0.2470,0.0724,0.7167,0.0199</t>
-  </si>
-  <si>
-    <t>0.6414,0.0023,0.4515,0.0035</t>
-  </si>
-  <si>
-    <t>0.0073,0.1776,0.9781,0.0013</t>
-  </si>
-  <si>
-    <t>0.0180,0.9080,0.1297,0.0026</t>
-  </si>
-  <si>
-    <t>0.0554,0.0366,0.8998,0.0142</t>
-  </si>
-  <si>
-    <t>0.0529,0.0671,0.0029,0.9114</t>
-  </si>
-  <si>
-    <t>0.0056,0.9830,0.0077,0.0041</t>
-  </si>
-  <si>
-    <t>0.0096,0.9705,0.0126,0.0039</t>
-  </si>
-  <si>
-    <t>0.0002,0.9976,0.0042,0.0030</t>
-  </si>
-  <si>
-    <t>0.0048,0.0278,0.9886,0.0017</t>
-  </si>
-  <si>
-    <t>0.0033,0.0605,0.9815,0.0017</t>
-  </si>
-  <si>
-    <t>0.0332,0.0022,0.9784,0.0004</t>
-  </si>
-  <si>
-    <t>0.0517,0.0015,0.9629,0.0008</t>
-  </si>
-  <si>
-    <t>0.0187,0.0014,0.9851,0.0002</t>
-  </si>
-  <si>
-    <t>0.0548,0.0082,0.9594,0.0002</t>
-  </si>
-  <si>
-    <t>0.9541,0.0894,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9913,0.0028,0.0029,0.0006</t>
-  </si>
-  <si>
-    <t>0.9903,0.0056,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.0029,0.0032,0.9915,0.0080</t>
-  </si>
-  <si>
-    <t>0.9921,0.0036,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9972,0.0010,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.7441,0.4548,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.0074,0.8271,0.8495,0.0046</t>
-  </si>
-  <si>
-    <t>0.0082,0.0047,0.9888,0.0014</t>
-  </si>
-  <si>
-    <t>0.0029,0.1213,0.9262,0.0516</t>
-  </si>
-  <si>
-    <t>0.0005,0.9509,0.9858,0.0003</t>
-  </si>
-  <si>
-    <t>0.0035,0.0006,0.9901,0.0032</t>
-  </si>
-  <si>
-    <t>0.0084,0.9845,0.0040,0.0029</t>
-  </si>
-  <si>
-    <t>0.0134,0.9871,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.9207,0.0054,0.1257,0.0012</t>
-  </si>
-  <si>
-    <t>0.4764,0.3771,0.2757,0.0100</t>
-  </si>
-  <si>
-    <t>0.0169,0.0118,0.9791,0.0034</t>
-  </si>
-  <si>
-    <t>0.0043,0.9552,0.3538,0.0011</t>
-  </si>
-  <si>
-    <t>0.0028,0.9839,0.0858,0.0005</t>
-  </si>
-  <si>
-    <t>0.0068,0.9901,0.0077,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9411,0.9572,0.0013</t>
-  </si>
-  <si>
-    <t>0.0097,0.0003,0.0035,0.9938</t>
-  </si>
-  <si>
-    <t>0.0005,0.0003,0.0002,0.9995</t>
-  </si>
-  <si>
-    <t>0.0130,0.0012,0.0001,0.9954</t>
-  </si>
-  <si>
-    <t>0.0102,0.0014,0.0003,0.9957</t>
-  </si>
-  <si>
-    <t>0.0106,0.0007,0.0056,0.9917</t>
-  </si>
-  <si>
-    <t>0.0017,0.0025,0.0001,0.9986</t>
-  </si>
-  <si>
-    <t>0.0168,0.9584,0.1081,0.0029</t>
-  </si>
-  <si>
-    <t>0.0051,0.8648,0.9158,0.0012</t>
-  </si>
-  <si>
-    <t>0.0143,0.7696,0.6366,0.0021</t>
-  </si>
-  <si>
-    <t>0.0018,0.6671,0.9759,0.0013</t>
-  </si>
-  <si>
-    <t>0.0027,0.9733,0.6632,0.0004</t>
-  </si>
-  <si>
-    <t>0.0031,0.8186,0.8407,0.0024</t>
-  </si>
-  <si>
-    <t>0.9982,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9953,0.0028,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9017,0.1086,0.0034,0.0036</t>
-  </si>
-  <si>
-    <t>0.9959,0.0014,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9844,0.0137,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.9976,0.0018,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0027,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9899,0.0096,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0018,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0003,0.0001,0.0008</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9756,0.0029,0.0162,0.0022</t>
+  </si>
+  <si>
+    <t>0.0017,0.0001,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.9655,0.0037,0.0005,0.0210</t>
+  </si>
+  <si>
+    <t>0.0845,0.0034,0.0004,0.9753</t>
+  </si>
+  <si>
+    <t>0.9986,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0014,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9876,0.0131,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9777,0.0282,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9972,0.0012,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.7713,0.0234,0.2971,0.0020</t>
+  </si>
+  <si>
+    <t>0.0916,0.0244,0.9118,0.0068</t>
+  </si>
+  <si>
+    <t>0.3630,0.0033,0.8632,0.0000</t>
+  </si>
+  <si>
+    <t>0.0407,0.0114,0.9395,0.0079</t>
+  </si>
+  <si>
+    <t>0.8807,0.0601,0.0813,0.0026</t>
+  </si>
+  <si>
+    <t>0.0051,0.9892,0.0047,0.0028</t>
+  </si>
+  <si>
+    <t>0.0027,0.9933,0.0074,0.0003</t>
+  </si>
+  <si>
+    <t>0.1470,0.9036,0.0091,0.0008</t>
+  </si>
+  <si>
+    <t>0.0005,0.9983,0.0018,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.9966,0.0094,0.0001</t>
+  </si>
+  <si>
+    <t>0.9415,0.0005,0.0864,0.0003</t>
+  </si>
+  <si>
+    <t>0.8690,0.0056,0.1472,0.0020</t>
+  </si>
+  <si>
+    <t>0.0049,0.0010,0.9931,0.0004</t>
+  </si>
+  <si>
+    <t>0.1112,0.0083,0.9081,0.0018</t>
+  </si>
+  <si>
+    <t>0.0692,0.0024,0.9512,0.0020</t>
+  </si>
+  <si>
+    <t>0.0267,0.0011,0.9728,0.0021</t>
+  </si>
+  <si>
+    <t>0.0014,0.0003,0.9974,0.0002</t>
+  </si>
+  <si>
+    <t>0.2084,0.8459,0.0121,0.0058</t>
+  </si>
+  <si>
+    <t>0.6307,0.2019,0.2548,0.0179</t>
+  </si>
+  <si>
+    <t>0.0236,0.0438,0.9665,0.0022</t>
+  </si>
+  <si>
+    <t>0.1785,0.8102,0.0144,0.0044</t>
+  </si>
+  <si>
+    <t>0.9334,0.0222,0.0038,0.0182</t>
+  </si>
+  <si>
+    <t>0.6988,0.0609,0.2777,0.0072</t>
+  </si>
+  <si>
+    <t>0.6705,0.4851,0.0218,0.0013</t>
+  </si>
+  <si>
+    <t>0.0043,0.9916,0.0217,0.0006</t>
+  </si>
+  <si>
+    <t>0.0315,0.6318,0.2679,0.0376</t>
+  </si>
+  <si>
+    <t>0.8109,0.0053,0.2906,0.0017</t>
+  </si>
+  <si>
+    <t>0.2462,0.0096,0.7780,0.0129</t>
+  </si>
+  <si>
+    <t>0.5726,0.0024,0.5780,0.0014</t>
+  </si>
+  <si>
+    <t>0.0059,0.1308,0.9808,0.0004</t>
+  </si>
+  <si>
+    <t>0.0096,0.9666,0.0127,0.0015</t>
+  </si>
+  <si>
+    <t>0.0069,0.0039,0.9853,0.0027</t>
+  </si>
+  <si>
+    <t>0.0096,0.6002,0.0015,0.7828</t>
+  </si>
+  <si>
+    <t>0.0026,0.9875,0.0030,0.0038</t>
+  </si>
+  <si>
+    <t>0.0089,0.9809,0.0096,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.9967,0.0022,0.0031</t>
+  </si>
+  <si>
+    <t>0.0002,0.1523,0.9951,0.0012</t>
+  </si>
+  <si>
+    <t>0.0221,0.0897,0.9194,0.0038</t>
+  </si>
+  <si>
+    <t>0.0670,0.0019,0.9669,0.0002</t>
+  </si>
+  <si>
+    <t>0.0062,0.0006,0.9904,0.0010</t>
+  </si>
+  <si>
+    <t>0.0013,0.0160,0.9938,0.0007</t>
+  </si>
+  <si>
+    <t>0.0764,0.0464,0.8965,0.0009</t>
+  </si>
+  <si>
+    <t>0.9165,0.1467,0.0029,0.0003</t>
+  </si>
+  <si>
+    <t>0.9629,0.0109,0.0298,0.0011</t>
+  </si>
+  <si>
+    <t>0.9948,0.0015,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.0030,0.0129,0.9938,0.0028</t>
+  </si>
+  <si>
+    <t>0.9780,0.0289,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9868,0.0095,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.0054,0.8404,0.8971,0.0024</t>
+  </si>
+  <si>
+    <t>0.0050,0.0040,0.9946,0.0004</t>
+  </si>
+  <si>
+    <t>0.0130,0.2886,0.6244,0.0422</t>
+  </si>
+  <si>
+    <t>0.0004,0.8779,0.9934,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.0012,0.9953,0.0011</t>
+  </si>
+  <si>
+    <t>0.0013,0.9933,0.0012,0.0068</t>
+  </si>
+  <si>
+    <t>0.0048,0.9933,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9965,0.0005,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.0528,0.0167,0.9664,0.0025</t>
+  </si>
+  <si>
+    <t>0.0061,0.0832,0.9818,0.0020</t>
+  </si>
+  <si>
+    <t>0.0019,0.9669,0.5763,0.0022</t>
+  </si>
+  <si>
+    <t>0.0016,0.9847,0.1621,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.9934,0.3556,0.0003</t>
+  </si>
+  <si>
+    <t>0.0021,0.9453,0.9200,0.0020</t>
+  </si>
+  <si>
+    <t>0.0312,0.0007,0.0106,0.9789</t>
+  </si>
+  <si>
+    <t>0.0013,0.0005,0.0002,0.9991</t>
+  </si>
+  <si>
+    <t>0.0190,0.0009,0.0001,0.9954</t>
+  </si>
+  <si>
+    <t>0.0620,0.0040,0.0047,0.9726</t>
+  </si>
+  <si>
+    <t>0.0067,0.0001,0.0011,0.9967</t>
+  </si>
+  <si>
+    <t>0.0005,0.0034,0.0002,0.9992</t>
+  </si>
+  <si>
+    <t>0.0139,0.9444,0.2082,0.0066</t>
+  </si>
+  <si>
+    <t>0.0048,0.9200,0.8225,0.0012</t>
+  </si>
+  <si>
+    <t>0.0758,0.3129,0.6502,0.0010</t>
+  </si>
+  <si>
+    <t>0.0085,0.2934,0.9426,0.0006</t>
+  </si>
+  <si>
+    <t>0.0009,0.9735,0.8719,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.9341,0.3222,0.0044</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9872,0.0145,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9937,0.0020,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9981,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9723,0.0316,0.0012,0.0009</t>
+  </si>
+  <si>
+    <t>0.9984,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9937,0.0032,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9960,0.0024,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9837,0.0226,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0006,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0048,0.0006,0.9938,0.0005</t>
+  </si>
+  <si>
+    <t>0.0215,0.0020,0.9790,0.0013</t>
+  </si>
+  <si>
+    <t>0.9879,0.0006,0.0071,0.0003</t>
+  </si>
+  <si>
+    <t>0.0468,0.0039,0.9603,0.0014</t>
+  </si>
+  <si>
+    <t>0.0050,0.9879,0.0082,0.0020</t>
+  </si>
+  <si>
+    <t>0.0037,0.9910,0.0081,0.0007</t>
+  </si>
+  <si>
+    <t>0.1012,0.9083,0.0309,0.0021</t>
+  </si>
+  <si>
+    <t>0.0040,0.9919,0.0049,0.0024</t>
+  </si>
+  <si>
+    <t>0.0168,0.9776,0.0226,0.0007</t>
+  </si>
+  <si>
+    <t>0.0028,0.9942,0.0043,0.0005</t>
+  </si>
+  <si>
+    <t>0.0337,0.9691,0.0043,0.0011</t>
+  </si>
+  <si>
+    <t>0.4792,0.3337,0.2382,0.0067</t>
+  </si>
+  <si>
+    <t>0.2994,0.0092,0.8154,0.0015</t>
+  </si>
+  <si>
+    <t>0.4915,0.2130,0.2296,0.0040</t>
+  </si>
+  <si>
+    <t>0.7595,0.0460,0.2458,0.0152</t>
+  </si>
+  <si>
+    <t>0.0692,0.0703,0.0374,0.9175</t>
+  </si>
+  <si>
+    <t>0.0025,0.9917,0.0019,0.0016</t>
+  </si>
+  <si>
+    <t>0.0004,0.9967,0.0003,0.0026</t>
+  </si>
+  <si>
+    <t>0.0045,0.9799,0.0045,0.0366</t>
+  </si>
+  <si>
+    <t>0.0011,0.9879,0.7519,0.0006</t>
+  </si>
+  <si>
+    <t>0.0030,0.9923,0.0283,0.0002</t>
+  </si>
+  <si>
+    <t>0.4173,0.7189,0.0104,0.0031</t>
+  </si>
+  <si>
+    <t>0.5069,0.5478,0.0564,0.0032</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9960,0.0011,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9985,0.0004,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9826,0.0043,0.0017,0.0060</t>
+  </si>
+  <si>
+    <t>0.9948,0.0012,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9972,0.0014,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9872,0.0051,0.0003,0.0017</t>
+  </si>
+  <si>
+    <t>0.9967,0.0007,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.0060,0.8714,0.8001,0.0050</t>
+  </si>
+  <si>
+    <t>0.0074,0.8375,0.8374,0.0013</t>
+  </si>
+  <si>
+    <t>0.0145,0.0247,0.9782,0.0003</t>
+  </si>
+  <si>
+    <t>0.0798,0.0152,0.9404,0.0004</t>
+  </si>
+  <si>
+    <t>0.9960,0.0003,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.5415,0.0129,0.6318,0.0022</t>
+  </si>
+  <si>
+    <t>0.0264,0.0003,0.9806,0.0008</t>
+  </si>
+  <si>
+    <t>0.9156,0.0123,0.1102,0.0016</t>
+  </si>
+  <si>
+    <t>0.3813,0.0009,0.0013,0.8664</t>
+  </si>
+  <si>
+    <t>0.0002,0.0010,0.0048,0.9988</t>
+  </si>
+  <si>
+    <t>0.0009,0.0082,0.0003,0.9987</t>
+  </si>
+  <si>
+    <t>0.0112,0.0002,0.0002,0.9971</t>
+  </si>
+  <si>
+    <t>0.0040,0.7151,0.5616,0.0219</t>
+  </si>
+  <si>
+    <t>0.9901,0.0030,0.0030,0.0006</t>
+  </si>
+  <si>
+    <t>0.0200,0.9686,0.0016,0.0128</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0878,0.9076,0.0030,0.0064</t>
+  </si>
+  <si>
+    <t>0.9963,0.0005,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.7914,0.0017,0.0006,0.4307</t>
+  </si>
+  <si>
+    <t>0.9954,0.0007,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.0100,0.0175,0.9856,0.0037</t>
+  </si>
+  <si>
+    <t>0.9201,0.0013,0.0026,0.0876</t>
+  </si>
+  <si>
+    <t>0.9525,0.0046,0.0009,0.0301</t>
+  </si>
+  <si>
+    <t>0.0920,0.8991,0.0262,0.0075</t>
+  </si>
+  <si>
+    <t>0.9865,0.0054,0.0043,0.0006</t>
+  </si>
+  <si>
+    <t>0.9890,0.0041,0.0061,0.0002</t>
+  </si>
+  <si>
+    <t>0.1100,0.7780,0.1289,0.0360</t>
+  </si>
+  <si>
+    <t>0.4158,0.0403,0.6807,0.0040</t>
+  </si>
+  <si>
+    <t>0.9900,0.0074,0.0022,0.0001</t>
   </si>
   <si>
     <t>0.9995,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.0301,0.0004,0.9763,0.0008</t>
-  </si>
-  <si>
-    <t>0.0260,0.0038,0.9783,0.0007</t>
-  </si>
-  <si>
-    <t>0.9845,0.0016,0.0022,0.0030</t>
-  </si>
-  <si>
-    <t>0.0764,0.0012,0.9474,0.0013</t>
-  </si>
-  <si>
-    <t>0.0114,0.9775,0.0097,0.0049</t>
-  </si>
-  <si>
-    <t>0.0081,0.9877,0.0055,0.0009</t>
-  </si>
-  <si>
-    <t>0.0418,0.9675,0.0061,0.0006</t>
-  </si>
-  <si>
-    <t>0.0070,0.9875,0.0037,0.0008</t>
-  </si>
-  <si>
-    <t>0.0025,0.9934,0.0158,0.0014</t>
-  </si>
-  <si>
-    <t>0.0018,0.9954,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.0235,0.9723,0.0053,0.0017</t>
-  </si>
-  <si>
-    <t>0.7084,0.0176,0.3672,0.0095</t>
-  </si>
-  <si>
-    <t>0.2814,0.0029,0.8414,0.0012</t>
-  </si>
-  <si>
-    <t>0.1685,0.6587,0.2762,0.0119</t>
-  </si>
-  <si>
-    <t>0.2775,0.0712,0.5822,0.1591</t>
-  </si>
-  <si>
-    <t>0.1030,0.0365,0.0202,0.8947</t>
-  </si>
-  <si>
-    <t>0.0023,0.9913,0.0040,0.0016</t>
-  </si>
-  <si>
-    <t>0.0007,0.9968,0.0003,0.0014</t>
-  </si>
-  <si>
-    <t>0.0014,0.9929,0.0009,0.0239</t>
-  </si>
-  <si>
-    <t>0.0029,0.9898,0.1540,0.0012</t>
-  </si>
-  <si>
-    <t>0.0011,0.9966,0.0230,0.0002</t>
-  </si>
-  <si>
-    <t>0.1708,0.8741,0.0299,0.0013</t>
-  </si>
-  <si>
-    <t>0.8749,0.2338,0.0059,0.0009</t>
-  </si>
-  <si>
-    <t>0.9952,0.0010,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9956,0.0007,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.9964,0.0014,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9958,0.0013,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0007,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9962,0.0011,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9937,0.0024,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.0035,0.8598,0.6951,0.0049</t>
-  </si>
-  <si>
-    <t>0.0009,0.9658,0.8734,0.0006</t>
-  </si>
-  <si>
-    <t>0.0122,0.0135,0.9860,0.0004</t>
-  </si>
-  <si>
-    <t>0.0837,0.0512,0.8832,0.0063</t>
-  </si>
-  <si>
-    <t>0.9984,0.0002,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9104,0.0070,0.1221,0.0015</t>
-  </si>
-  <si>
-    <t>0.0585,0.0021,0.9513,0.0023</t>
-  </si>
-  <si>
-    <t>0.9018,0.0490,0.0543,0.0056</t>
-  </si>
-  <si>
-    <t>0.4193,0.0003,0.0001,0.8791</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.0066,0.9993</t>
-  </si>
-  <si>
-    <t>0.0006,0.0115,0.0011,0.9982</t>
-  </si>
-  <si>
-    <t>0.0087,0.0004,0.0004,0.9958</t>
-  </si>
-  <si>
-    <t>0.0101,0.7447,0.7479,0.0044</t>
-  </si>
-  <si>
-    <t>0.9953,0.0017,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.0715,0.9389,0.0008,0.0027</t>
-  </si>
-  <si>
-    <t>0.9952,0.0013,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.2597,0.7901,0.0052,0.0066</t>
-  </si>
-  <si>
-    <t>0.9948,0.0013,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.7899,0.0118,0.0174,0.2197</t>
-  </si>
-  <si>
-    <t>0.9953,0.0012,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.1148,0.9937,0.0073</t>
-  </si>
-  <si>
-    <t>0.9706,0.0002,0.0008,0.0367</t>
-  </si>
-  <si>
-    <t>0.9888,0.0008,0.0008,0.0059</t>
-  </si>
-  <si>
-    <t>0.7236,0.2829,0.0207,0.0049</t>
-  </si>
-  <si>
-    <t>0.9809,0.0118,0.0043,0.0007</t>
-  </si>
-  <si>
-    <t>0.9730,0.0176,0.0095,0.0015</t>
-  </si>
-  <si>
-    <t>0.1994,0.8115,0.0059,0.0070</t>
-  </si>
-  <si>
-    <t>0.8352,0.0796,0.0921,0.0031</t>
-  </si>
-  <si>
-    <t>0.9781,0.0169,0.0055,0.0006</t>
-  </si>
-  <si>
-    <t>0.9961,0.0010,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9961,0.0019,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9917,0.0042,0.0024,0.0004</t>
-  </si>
-  <si>
-    <t>0.9958,0.0007,0.0021,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9823,0.0148,0.0027,0.0007</t>
-  </si>
-  <si>
-    <t>0.9964,0.0008,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9980,0.0003,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.8647,0.1666,0.0109,0.0005</t>
-  </si>
-  <si>
-    <t>0.9631,0.0414,0.0047,0.0012</t>
-  </si>
-  <si>
-    <t>0.5962,0.4877,0.0087,0.0022</t>
-  </si>
-  <si>
-    <t>0.9403,0.0263,0.0362,0.0014</t>
-  </si>
-  <si>
-    <t>0.9777,0.0356,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9923,0.0035,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.9878,0.0033,0.0088,0.0007</t>
-  </si>
-  <si>
-    <t>0.8600,0.2724,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.0203,0.0102,0.9858,0.0005</t>
-  </si>
-  <si>
-    <t>0.9557,0.0430,0.0053,0.0015</t>
-  </si>
-  <si>
-    <t>0.0091,0.0014,0.9880,0.0006</t>
-  </si>
-  <si>
-    <t>0.0201,0.0405,0.9629,0.0024</t>
-  </si>
-  <si>
-    <t>0.0139,0.0007,0.9907,0.0002</t>
-  </si>
-  <si>
-    <t>0.0107,0.0054,0.9812,0.0018</t>
-  </si>
-  <si>
-    <t>0.0041,0.0019,0.9932,0.0007</t>
-  </si>
-  <si>
-    <t>0.0191,0.0006,0.9909,0.0000</t>
-  </si>
-  <si>
-    <t>0.0043,0.0054,0.9920,0.0016</t>
-  </si>
-  <si>
-    <t>0.2161,0.0098,0.8713,0.0016</t>
-  </si>
-  <si>
-    <t>0.4679,0.0079,0.7405,0.0011</t>
-  </si>
-  <si>
-    <t>0.6724,0.0320,0.3949,0.0136</t>
-  </si>
-  <si>
-    <t>0.1636,0.0106,0.9001,0.0022</t>
-  </si>
-  <si>
-    <t>0.1258,0.4154,0.5383,0.0039</t>
-  </si>
-  <si>
-    <t>0.4967,0.0621,0.4828,0.0010</t>
-  </si>
-  <si>
-    <t>0.9408,0.0041,0.0854,0.0012</t>
-  </si>
-  <si>
-    <t>0.4963,0.0124,0.7133,0.0050</t>
-  </si>
-  <si>
-    <t>0.0249,0.9727,0.0081,0.0008</t>
-  </si>
-  <si>
-    <t>0.1046,0.9392,0.0078,0.0002</t>
-  </si>
-  <si>
-    <t>0.2679,0.7597,0.0241,0.0016</t>
-  </si>
-  <si>
-    <t>0.7960,0.2940,0.0064,0.0002</t>
-  </si>
-  <si>
-    <t>0.9127,0.1479,0.0027,0.0006</t>
-  </si>
-  <si>
-    <t>0.7973,0.2259,0.0155,0.0011</t>
-  </si>
-  <si>
-    <t>0.9884,0.0005,0.0138,0.0001</t>
-  </si>
-  <si>
-    <t>0.9125,0.0078,0.0605,0.0087</t>
-  </si>
-  <si>
-    <t>0.9453,0.0040,0.0541,0.0043</t>
-  </si>
-  <si>
-    <t>0.8855,0.0172,0.1203,0.0039</t>
-  </si>
-  <si>
-    <t>0.0102,0.0233,0.9749,0.0057</t>
-  </si>
-  <si>
-    <t>0.0981,0.0471,0.8661,0.0122</t>
-  </si>
-  <si>
-    <t>0.1065,0.0638,0.8863,0.0018</t>
-  </si>
-  <si>
-    <t>0.3632,0.0972,0.5527,0.0084</t>
-  </si>
-  <si>
-    <t>0.0038,0.7121,0.8355,0.0041</t>
-  </si>
-  <si>
-    <t>0.9949,0.0034,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9980,0.0011,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9790,0.0152,0.0040,0.0008</t>
-  </si>
-  <si>
-    <t>0.9958,0.0016,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9835,0.0129,0.0010,0.0009</t>
-  </si>
-  <si>
-    <t>0.9977,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0011,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0131,0.0035,0.9889,0.0007</t>
-  </si>
-  <si>
-    <t>0.1168,0.6457,0.3557,0.0398</t>
-  </si>
-  <si>
-    <t>0.9508,0.0035,0.0271,0.0068</t>
-  </si>
-  <si>
-    <t>0.0490,0.0011,0.9733,0.0002</t>
-  </si>
-  <si>
-    <t>0.0033,0.0034,0.9905,0.0009</t>
-  </si>
-  <si>
-    <t>0.1744,0.0119,0.8664,0.0011</t>
-  </si>
-  <si>
-    <t>0.0168,0.0029,0.9809,0.0014</t>
-  </si>
-  <si>
-    <t>0.0036,0.0058,0.9898,0.0025</t>
-  </si>
-  <si>
-    <t>0.0444,0.0047,0.9745,0.0004</t>
-  </si>
-  <si>
-    <t>0.0064,0.0035,0.9805,0.0082</t>
-  </si>
-  <si>
-    <t>0.0409,0.0573,0.9276,0.0040</t>
-  </si>
-  <si>
-    <t>0.7666,0.0049,0.3375,0.0022</t>
-  </si>
-  <si>
-    <t>0.8833,0.0024,0.1582,0.0026</t>
-  </si>
-  <si>
-    <t>0.9707,0.0015,0.0381,0.0005</t>
-  </si>
-  <si>
-    <t>0.9865,0.0098,0.0004,0.0011</t>
-  </si>
-  <si>
-    <t>0.9961,0.0019,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9973,0.0012,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9937,0.0060,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9970,0.0019,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9948,0.0049,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9981,0.0011,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0009,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.0744,0.0022,0.9607,0.0001</t>
-  </si>
-  <si>
-    <t>0.0142,0.0326,0.9798,0.0005</t>
-  </si>
-  <si>
-    <t>0.0274,0.0256,0.9552,0.0084</t>
-  </si>
-  <si>
-    <t>0.0617,0.0255,0.9314,0.0034</t>
-  </si>
-  <si>
-    <t>0.0260,0.0012,0.9785,0.0005</t>
-  </si>
-  <si>
-    <t>0.0476,0.0020,0.9659,0.0005</t>
-  </si>
-  <si>
-    <t>0.0114,0.0038,0.9783,0.0081</t>
-  </si>
-  <si>
-    <t>0.5121,0.0026,0.6903,0.0008</t>
-  </si>
-  <si>
-    <t>0.9661,0.0003,0.0023,0.0269</t>
-  </si>
-  <si>
-    <t>0.1109,0.0148,0.0014,0.9507</t>
-  </si>
-  <si>
-    <t>0.0540,0.0016,0.0024,0.9728</t>
-  </si>
-  <si>
-    <t>0.0020,0.0001,0.0005,0.9989</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.0028,0.9987</t>
-  </si>
-  <si>
-    <t>0.7587,0.0171,0.0122,0.2637</t>
+    <t>0.9984,0.0006,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9918,0.0042,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.9969,0.0005,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9967,0.0007,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9638,0.0394,0.0051,0.0007</t>
+  </si>
+  <si>
+    <t>0.9963,0.0005,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.5419,0.5743,0.0094,0.0020</t>
+  </si>
+  <si>
+    <t>0.4740,0.6930,0.0052,0.0006</t>
+  </si>
+  <si>
+    <t>0.0857,0.9205,0.0068,0.0028</t>
+  </si>
+  <si>
+    <t>0.8031,0.1008,0.1223,0.0357</t>
+  </si>
+  <si>
+    <t>0.9943,0.0030,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9898,0.0078,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.9951,0.0019,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.9299,0.0684,0.0137,0.0032</t>
+  </si>
+  <si>
+    <t>0.0036,0.0256,0.9934,0.0007</t>
+  </si>
+  <si>
+    <t>0.9758,0.0094,0.0074,0.0019</t>
+  </si>
+  <si>
+    <t>0.0152,0.0031,0.9857,0.0002</t>
+  </si>
+  <si>
+    <t>0.0138,0.0639,0.9678,0.0015</t>
+  </si>
+  <si>
+    <t>0.0085,0.0026,0.9851,0.0049</t>
+  </si>
+  <si>
+    <t>0.0383,0.0424,0.9434,0.0024</t>
+  </si>
+  <si>
+    <t>0.0022,0.0049,0.9952,0.0008</t>
+  </si>
+  <si>
+    <t>0.0076,0.0012,0.9931,0.0002</t>
+  </si>
+  <si>
+    <t>0.0056,0.0100,0.9915,0.0003</t>
+  </si>
+  <si>
+    <t>0.0541,0.0023,0.9689,0.0014</t>
+  </si>
+  <si>
+    <t>0.5563,0.0383,0.5269,0.0043</t>
+  </si>
+  <si>
+    <t>0.7340,0.0240,0.3389,0.0086</t>
+  </si>
+  <si>
+    <t>0.3224,0.1208,0.6495,0.0031</t>
+  </si>
+  <si>
+    <t>0.0976,0.5506,0.2551,0.0007</t>
+  </si>
+  <si>
+    <t>0.2071,0.0907,0.7350,0.0030</t>
+  </si>
+  <si>
+    <t>0.5059,0.0262,0.6701,0.0032</t>
+  </si>
+  <si>
+    <t>0.0779,0.0513,0.9045,0.0108</t>
+  </si>
+  <si>
+    <t>0.0107,0.9856,0.0073,0.0009</t>
+  </si>
+  <si>
+    <t>0.1430,0.9080,0.0066,0.0005</t>
+  </si>
+  <si>
+    <t>0.9408,0.0949,0.0021,0.0004</t>
+  </si>
+  <si>
+    <t>0.8768,0.1965,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9898,0.0089,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.6884,0.1988,0.1547,0.0106</t>
+  </si>
+  <si>
+    <t>0.9677,0.0007,0.0729,0.0002</t>
+  </si>
+  <si>
+    <t>0.5184,0.0674,0.4359,0.0534</t>
+  </si>
+  <si>
+    <t>0.8032,0.0039,0.3374,0.0007</t>
+  </si>
+  <si>
+    <t>0.5620,0.0338,0.5033,0.0062</t>
+  </si>
+  <si>
+    <t>0.0085,0.0088,0.9742,0.0145</t>
+  </si>
+  <si>
+    <t>0.0253,0.0323,0.9619,0.0013</t>
+  </si>
+  <si>
+    <t>0.3636,0.0649,0.6067,0.0309</t>
+  </si>
+  <si>
+    <t>0.0681,0.0151,0.9331,0.0045</t>
+  </si>
+  <si>
+    <t>0.0023,0.2940,0.9786,0.0007</t>
+  </si>
+  <si>
+    <t>0.9975,0.0005,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9920,0.0062,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.9951,0.0024,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9981,0.0005,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9825,0.0150,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.0021,0.0027,0.9968,0.0006</t>
+  </si>
+  <si>
+    <t>0.3331,0.2434,0.4312,0.0845</t>
+  </si>
+  <si>
+    <t>0.8373,0.0042,0.1640,0.0065</t>
+  </si>
+  <si>
+    <t>0.1885,0.0027,0.9002,0.0005</t>
+  </si>
+  <si>
+    <t>0.0074,0.0061,0.9900,0.0003</t>
+  </si>
+  <si>
+    <t>0.1020,0.0035,0.9442,0.0001</t>
+  </si>
+  <si>
+    <t>0.0300,0.0075,0.9684,0.0009</t>
+  </si>
+  <si>
+    <t>0.0330,0.0097,0.9531,0.0051</t>
+  </si>
+  <si>
+    <t>0.0294,0.0024,0.9784,0.0008</t>
+  </si>
+  <si>
+    <t>0.0431,0.0060,0.9325,0.0148</t>
+  </si>
+  <si>
+    <t>0.0175,0.1167,0.9481,0.0137</t>
+  </si>
+  <si>
+    <t>0.7687,0.0049,0.4035,0.0007</t>
+  </si>
+  <si>
+    <t>0.9348,0.0009,0.0930,0.0006</t>
+  </si>
+  <si>
+    <t>0.9532,0.0052,0.0494,0.0009</t>
+  </si>
+  <si>
+    <t>0.9871,0.0113,0.0019,0.0009</t>
+  </si>
+  <si>
+    <t>0.9946,0.0029,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9958,0.0026,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9955,0.0022,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9796,0.0248,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.9937,0.0056,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.0051,0.0262,0.9830,0.0007</t>
+  </si>
+  <si>
+    <t>0.0117,0.0185,0.9824,0.0004</t>
+  </si>
+  <si>
+    <t>0.0188,0.0212,0.9707,0.0043</t>
+  </si>
+  <si>
+    <t>0.0245,0.0352,0.9502,0.0026</t>
+  </si>
+  <si>
+    <t>0.0131,0.0013,0.9882,0.0002</t>
+  </si>
+  <si>
+    <t>0.0320,0.0037,0.9602,0.0041</t>
+  </si>
+  <si>
+    <t>0.1379,0.0155,0.8587,0.0226</t>
+  </si>
+  <si>
+    <t>0.1082,0.0089,0.8451,0.0121</t>
+  </si>
+  <si>
+    <t>0.8187,0.0054,0.0199,0.1692</t>
+  </si>
+  <si>
+    <t>0.4291,0.0187,0.0071,0.6756</t>
+  </si>
+  <si>
+    <t>0.4945,0.0002,0.0002,0.8525</t>
+  </si>
+  <si>
+    <t>0.0040,0.0001,0.0005,0.9982</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0002,0.9995</t>
+  </si>
+  <si>
+    <t>0.7181,0.0446,0.0238,0.2883</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1973,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2001,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2141,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2155,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2169,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2281,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2295,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2323,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2337,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2379,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2407,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2446,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2491,7 @@
         <v>259</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2505,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2533,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2659,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2922,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2967,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2995,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3009,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3023,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3037,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3051,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3065,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3079,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3093,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3107,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3149,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3443,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3552,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3569,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3580,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3611,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3664,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3681,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3706,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3835,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3849,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3877,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3902,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3919,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3947,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3961,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3975,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3989,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4003,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4031,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4154,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4199,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4210,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4350,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4364,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4378,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4591,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4619,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4633,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4658,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4672,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4689,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4703,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4717,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4728,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4826,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4857,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4871,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4885,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>368</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5095,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5123,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5165,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5375,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5389,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5403,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5417,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5431,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5445,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5459,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5473,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5487,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5501,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
